--- a/CascadeProjects/windsurf-project/fantasy-trade-analyzer/data/audit_logs/adjustment_audit_log_Mr_Squidward’s_Gay_Layup_Line.xlsx
+++ b/CascadeProjects/windsurf-project/fantasy-trade-analyzer/data/audit_logs/adjustment_audit_log_Mr_Squidward’s_Gay_Layup_Line.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N214"/>
+  <dimension ref="A1:N326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="5" min="1" max="1"/>
@@ -10782,6 +10782,5494 @@
         <v>0</v>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>14</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>LAMELOcan Airlines Flight 11</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>z4ag3f5qmdgtlka8</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>25</v>
+      </c>
+      <c r="F215" t="n">
+        <v>25</v>
+      </c>
+      <c r="G215" t="n">
+        <v>1893</v>
+      </c>
+      <c r="H215" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
+        <v>1893</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>14</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>The Pentagon</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>wjjl8qwsmdgtlka2</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>25</v>
+      </c>
+      <c r="F216" t="n">
+        <v>25</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1636</v>
+      </c>
+      <c r="H216" t="n">
+        <v>65.44</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
+        <v>1636</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>14</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Daaaaaa Jankees lose</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>7wets94rmdgtlkaa</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>25</v>
+      </c>
+      <c r="F217" t="n">
+        <v>27</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H217" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="I217" t="n">
+        <v>2</v>
+      </c>
+      <c r="J217" s="7" t="n">
+        <v>117.12</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>7.41%</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>1463.88</v>
+      </c>
+      <c r="M217" t="n">
+        <v>-117</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>14</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>The Noto Son</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>zjydlxwhmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>25</v>
+      </c>
+      <c r="F218" t="n">
+        <v>25</v>
+      </c>
+      <c r="G218" t="n">
+        <v>1561</v>
+      </c>
+      <c r="H218" t="n">
+        <v>62.44</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
+        <v>1561</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>14</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>President of Retarded Operations</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>4trk7d98mdgtlkab</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>25</v>
+      </c>
+      <c r="F219" t="n">
+        <v>26</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1554</v>
+      </c>
+      <c r="H219" t="n">
+        <v>59.77</v>
+      </c>
+      <c r="I219" t="n">
+        <v>1</v>
+      </c>
+      <c r="J219" s="7" t="n">
+        <v>59.77</v>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>1494.23</v>
+      </c>
+      <c r="M219" t="n">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>14</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>A Stupid Silly Cat</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>0l1gmqj7mdgtlka6</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>25</v>
+      </c>
+      <c r="F220" t="n">
+        <v>25</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1482</v>
+      </c>
+      <c r="H220" t="n">
+        <v>59.28</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L220" t="n">
+        <v>1482</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>14</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>George W Bush</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>3s2b2okkmdgtlka5</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>25</v>
+      </c>
+      <c r="F221" t="n">
+        <v>25</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1478</v>
+      </c>
+      <c r="H221" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>1478</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>14</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>I'm Your Uber Driver</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>lc47vt4pmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>25</v>
+      </c>
+      <c r="F222" t="n">
+        <v>25</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1451</v>
+      </c>
+      <c r="H222" t="n">
+        <v>58.04</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>1451</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>14</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Kamala's Gunz</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>hxzn4i3jmdgtlka7</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>25</v>
+      </c>
+      <c r="F223" t="n">
+        <v>26</v>
+      </c>
+      <c r="G223" t="n">
+        <v>1418</v>
+      </c>
+      <c r="H223" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="I223" t="n">
+        <v>1</v>
+      </c>
+      <c r="J223" s="7" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>1363.46</v>
+      </c>
+      <c r="M223" t="n">
+        <v>-55</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>14</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Jesus Christ</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>zh45p7homdgtlka1</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>25</v>
+      </c>
+      <c r="F224" t="n">
+        <v>25</v>
+      </c>
+      <c r="G224" t="n">
+        <v>1380</v>
+      </c>
+      <c r="H224" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L224" t="n">
+        <v>1380</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>14</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>9/11 Second Tower</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>68fvh5u4mdgtlka8</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>25</v>
+      </c>
+      <c r="F225" t="n">
+        <v>25</v>
+      </c>
+      <c r="G225" t="n">
+        <v>1358</v>
+      </c>
+      <c r="H225" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L225" t="n">
+        <v>1358</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>14</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>PartyMarty__</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>oi0ae85dmdmdspm2</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>25</v>
+      </c>
+      <c r="F226" t="n">
+        <v>31</v>
+      </c>
+      <c r="G226" t="n">
+        <v>1323</v>
+      </c>
+      <c r="H226" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="I226" t="n">
+        <v>6</v>
+      </c>
+      <c r="J226" s="7" t="n">
+        <v>256.08</v>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>19.36%</t>
+        </is>
+      </c>
+      <c r="L226" t="n">
+        <v>1066.92</v>
+      </c>
+      <c r="M226" t="n">
+        <v>-256</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>14</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Haliban’s Heroes</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>rhb3mk9hmdgtlka9</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>25</v>
+      </c>
+      <c r="F227" t="n">
+        <v>25</v>
+      </c>
+      <c r="G227" t="n">
+        <v>1267</v>
+      </c>
+      <c r="H227" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L227" t="n">
+        <v>1267</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>14</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Kevin O’Leary</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>467wxistmdgtlka3</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>25</v>
+      </c>
+      <c r="F228" t="n">
+        <v>25</v>
+      </c>
+      <c r="G228" t="n">
+        <v>1258</v>
+      </c>
+      <c r="H228" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L228" t="n">
+        <v>1258</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>14</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>CaitlinClark KeepsItHairy</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>qmjw5ehtmduykj4n</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>25</v>
+      </c>
+      <c r="F229" t="n">
+        <v>28</v>
+      </c>
+      <c r="G229" t="n">
+        <v>1164</v>
+      </c>
+      <c r="H229" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="I229" t="n">
+        <v>3</v>
+      </c>
+      <c r="J229" s="7" t="n">
+        <v>124.71</v>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>10.71%</t>
+        </is>
+      </c>
+      <c r="L229" t="n">
+        <v>1039.29</v>
+      </c>
+      <c r="M229" t="n">
+        <v>-125</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>14</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>9/11 First Tower</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>dmx5bjkpmdgtlkab</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>25</v>
+      </c>
+      <c r="F230" t="n">
+        <v>23</v>
+      </c>
+      <c r="G230" t="n">
+        <v>925</v>
+      </c>
+      <c r="H230" t="n">
+        <v>40.22</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L230" t="n">
+        <v>925</v>
+      </c>
+      <c r="M230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>15</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>A Stupid Silly Cat</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>0l1gmqj7mdgtlka6</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>25</v>
+      </c>
+      <c r="F231" t="n">
+        <v>25</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1595</v>
+      </c>
+      <c r="H231" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L231" t="n">
+        <v>1595</v>
+      </c>
+      <c r="M231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>15</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>LAMELOcan Airlines Flight 11</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>z4ag3f5qmdgtlka8</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>25</v>
+      </c>
+      <c r="F232" t="n">
+        <v>27</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1542</v>
+      </c>
+      <c r="H232" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="I232" t="n">
+        <v>2</v>
+      </c>
+      <c r="J232" s="7" t="n">
+        <v>114.22</v>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>7.41%</t>
+        </is>
+      </c>
+      <c r="L232" t="n">
+        <v>1427.78</v>
+      </c>
+      <c r="M232" t="n">
+        <v>-114</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>15</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>The Pentagon</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>wjjl8qwsmdgtlka2</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>25</v>
+      </c>
+      <c r="F233" t="n">
+        <v>25</v>
+      </c>
+      <c r="G233" t="n">
+        <v>1507</v>
+      </c>
+      <c r="H233" t="n">
+        <v>60.28</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L233" t="n">
+        <v>1507</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>15</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>President of Retarded Operations</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>4trk7d98mdgtlkab</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>25</v>
+      </c>
+      <c r="F234" t="n">
+        <v>26</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1506</v>
+      </c>
+      <c r="H234" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="I234" t="n">
+        <v>1</v>
+      </c>
+      <c r="J234" s="7" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L234" t="n">
+        <v>1448.08</v>
+      </c>
+      <c r="M234" t="n">
+        <v>-58</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>15</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>The Noto Son</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>zjydlxwhmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>25</v>
+      </c>
+      <c r="F235" t="n">
+        <v>25</v>
+      </c>
+      <c r="G235" t="n">
+        <v>1457</v>
+      </c>
+      <c r="H235" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L235" t="n">
+        <v>1457</v>
+      </c>
+      <c r="M235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>15</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Kevin O’Leary</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>467wxistmdgtlka3</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>25</v>
+      </c>
+      <c r="F236" t="n">
+        <v>25</v>
+      </c>
+      <c r="G236" t="n">
+        <v>1393</v>
+      </c>
+      <c r="H236" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L236" t="n">
+        <v>1393</v>
+      </c>
+      <c r="M236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>15</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>I'm Your Uber Driver</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>lc47vt4pmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>25</v>
+      </c>
+      <c r="F237" t="n">
+        <v>25</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1372</v>
+      </c>
+      <c r="H237" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L237" t="n">
+        <v>1372</v>
+      </c>
+      <c r="M237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>15</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Haliban’s Heroes</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>rhb3mk9hmdgtlka9</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>25</v>
+      </c>
+      <c r="F238" t="n">
+        <v>25</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1353</v>
+      </c>
+      <c r="H238" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L238" t="n">
+        <v>1353</v>
+      </c>
+      <c r="M238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>15</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>PartyMarty__</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>oi0ae85dmdmdspm2</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>25</v>
+      </c>
+      <c r="F239" t="n">
+        <v>27</v>
+      </c>
+      <c r="G239" t="n">
+        <v>1347</v>
+      </c>
+      <c r="H239" t="n">
+        <v>49.89</v>
+      </c>
+      <c r="I239" t="n">
+        <v>2</v>
+      </c>
+      <c r="J239" s="7" t="n">
+        <v>99.78</v>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>7.41%</t>
+        </is>
+      </c>
+      <c r="L239" t="n">
+        <v>1247.22</v>
+      </c>
+      <c r="M239" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>15</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>9/11 Second Tower</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>68fvh5u4mdgtlka8</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>25</v>
+      </c>
+      <c r="F240" t="n">
+        <v>26</v>
+      </c>
+      <c r="G240" t="n">
+        <v>1344</v>
+      </c>
+      <c r="H240" t="n">
+        <v>51.69</v>
+      </c>
+      <c r="I240" t="n">
+        <v>1</v>
+      </c>
+      <c r="J240" s="7" t="n">
+        <v>51.69</v>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L240" t="n">
+        <v>1292.31</v>
+      </c>
+      <c r="M240" t="n">
+        <v>-52</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>15</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Daaaaaa Jankees lose</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>7wets94rmdgtlkaa</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>25</v>
+      </c>
+      <c r="F241" t="n">
+        <v>25</v>
+      </c>
+      <c r="G241" t="n">
+        <v>1210</v>
+      </c>
+      <c r="H241" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L241" t="n">
+        <v>1210</v>
+      </c>
+      <c r="M241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>15</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>George W Bush</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>3s2b2okkmdgtlka5</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>25</v>
+      </c>
+      <c r="F242" t="n">
+        <v>26</v>
+      </c>
+      <c r="G242" t="n">
+        <v>1208</v>
+      </c>
+      <c r="H242" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="I242" t="n">
+        <v>1</v>
+      </c>
+      <c r="J242" s="7" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L242" t="n">
+        <v>1161.54</v>
+      </c>
+      <c r="M242" t="n">
+        <v>-46</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>15</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Jesus Christ</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>zh45p7homdgtlka1</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>25</v>
+      </c>
+      <c r="F243" t="n">
+        <v>23</v>
+      </c>
+      <c r="G243" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H243" t="n">
+        <v>50</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L243" t="n">
+        <v>1150</v>
+      </c>
+      <c r="M243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>15</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>9/11 First Tower</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>dmx5bjkpmdgtlkab</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>25</v>
+      </c>
+      <c r="F244" t="n">
+        <v>25</v>
+      </c>
+      <c r="G244" t="n">
+        <v>1123</v>
+      </c>
+      <c r="H244" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L244" t="n">
+        <v>1123</v>
+      </c>
+      <c r="M244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>15</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>CaitlinClark KeepsItHairy</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>qmjw5ehtmduykj4n</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>25</v>
+      </c>
+      <c r="F245" t="n">
+        <v>25</v>
+      </c>
+      <c r="G245" t="n">
+        <v>1075</v>
+      </c>
+      <c r="H245" t="n">
+        <v>43</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L245" t="n">
+        <v>1075</v>
+      </c>
+      <c r="M245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>15</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Kamala's Gunz</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>hxzn4i3jmdgtlka7</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>25</v>
+      </c>
+      <c r="F246" t="n">
+        <v>21</v>
+      </c>
+      <c r="G246" t="n">
+        <v>826</v>
+      </c>
+      <c r="H246" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L246" t="n">
+        <v>826</v>
+      </c>
+      <c r="M246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>16</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>9/11 Second Tower</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>68fvh5u4mdgtlka8</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>28</v>
+      </c>
+      <c r="F247" t="n">
+        <v>29</v>
+      </c>
+      <c r="G247" t="n">
+        <v>1869</v>
+      </c>
+      <c r="H247" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="I247" t="n">
+        <v>1</v>
+      </c>
+      <c r="J247" s="7" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="L247" t="n">
+        <v>1804.55</v>
+      </c>
+      <c r="M247" t="n">
+        <v>-64</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>16</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>The Pentagon</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>wjjl8qwsmdgtlka2</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>28</v>
+      </c>
+      <c r="F248" t="n">
+        <v>29</v>
+      </c>
+      <c r="G248" t="n">
+        <v>1841</v>
+      </c>
+      <c r="H248" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="I248" t="n">
+        <v>1</v>
+      </c>
+      <c r="J248" s="7" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="L248" t="n">
+        <v>1777.52</v>
+      </c>
+      <c r="M248" t="n">
+        <v>-63</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>16</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>LAMELOcan Airlines Flight 11</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>z4ag3f5qmdgtlka8</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>28</v>
+      </c>
+      <c r="F249" t="n">
+        <v>28</v>
+      </c>
+      <c r="G249" t="n">
+        <v>1714</v>
+      </c>
+      <c r="H249" t="n">
+        <v>61.21</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L249" t="n">
+        <v>1714</v>
+      </c>
+      <c r="M249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>16</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Haliban’s Heroes</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>rhb3mk9hmdgtlka9</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>28</v>
+      </c>
+      <c r="F250" t="n">
+        <v>28</v>
+      </c>
+      <c r="G250" t="n">
+        <v>1690</v>
+      </c>
+      <c r="H250" t="n">
+        <v>60.36</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L250" t="n">
+        <v>1690</v>
+      </c>
+      <c r="M250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>16</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Kevin O’Leary</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>467wxistmdgtlka3</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>28</v>
+      </c>
+      <c r="F251" t="n">
+        <v>28</v>
+      </c>
+      <c r="G251" t="n">
+        <v>1642</v>
+      </c>
+      <c r="H251" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L251" t="n">
+        <v>1642</v>
+      </c>
+      <c r="M251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>16</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>A Stupid Silly Cat</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>0l1gmqj7mdgtlka6</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>28</v>
+      </c>
+      <c r="F252" t="n">
+        <v>28</v>
+      </c>
+      <c r="G252" t="n">
+        <v>1625</v>
+      </c>
+      <c r="H252" t="n">
+        <v>58.04</v>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L252" t="n">
+        <v>1625</v>
+      </c>
+      <c r="M252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>16</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>The Noto Son</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>zjydlxwhmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>28</v>
+      </c>
+      <c r="F253" t="n">
+        <v>29</v>
+      </c>
+      <c r="G253" t="n">
+        <v>1560</v>
+      </c>
+      <c r="H253" t="n">
+        <v>53.79</v>
+      </c>
+      <c r="I253" t="n">
+        <v>1</v>
+      </c>
+      <c r="J253" s="7" t="n">
+        <v>53.79</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="L253" t="n">
+        <v>1506.21</v>
+      </c>
+      <c r="M253" t="n">
+        <v>-54</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>16</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>I'm Your Uber Driver</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>lc47vt4pmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>28</v>
+      </c>
+      <c r="F254" t="n">
+        <v>28</v>
+      </c>
+      <c r="G254" t="n">
+        <v>1555</v>
+      </c>
+      <c r="H254" t="n">
+        <v>55.54</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L254" t="n">
+        <v>1555</v>
+      </c>
+      <c r="M254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>16</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>PartyMarty__</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>oi0ae85dmdmdspm2</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>28</v>
+      </c>
+      <c r="F255" t="n">
+        <v>28</v>
+      </c>
+      <c r="G255" t="n">
+        <v>1520</v>
+      </c>
+      <c r="H255" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L255" t="n">
+        <v>1520</v>
+      </c>
+      <c r="M255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>16</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Daaaaaa Jankees lose</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>7wets94rmdgtlkaa</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>28</v>
+      </c>
+      <c r="F256" t="n">
+        <v>29</v>
+      </c>
+      <c r="G256" t="n">
+        <v>1509</v>
+      </c>
+      <c r="H256" t="n">
+        <v>52.03</v>
+      </c>
+      <c r="I256" t="n">
+        <v>1</v>
+      </c>
+      <c r="J256" s="7" t="n">
+        <v>52.03</v>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="L256" t="n">
+        <v>1456.97</v>
+      </c>
+      <c r="M256" t="n">
+        <v>-52</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>16</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>President of Retarded Operations</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>4trk7d98mdgtlkab</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>28</v>
+      </c>
+      <c r="F257" t="n">
+        <v>28</v>
+      </c>
+      <c r="G257" t="n">
+        <v>1470</v>
+      </c>
+      <c r="H257" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L257" t="n">
+        <v>1470</v>
+      </c>
+      <c r="M257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>16</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Kamala's Gunz</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>hxzn4i3jmdgtlka7</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>28</v>
+      </c>
+      <c r="F258" t="n">
+        <v>30</v>
+      </c>
+      <c r="G258" t="n">
+        <v>1456</v>
+      </c>
+      <c r="H258" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="I258" t="n">
+        <v>2</v>
+      </c>
+      <c r="J258" s="7" t="n">
+        <v>97.06</v>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>6.67%</t>
+        </is>
+      </c>
+      <c r="L258" t="n">
+        <v>1358.94</v>
+      </c>
+      <c r="M258" t="n">
+        <v>-97</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>16</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>9/11 First Tower</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>dmx5bjkpmdgtlkab</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>28</v>
+      </c>
+      <c r="F259" t="n">
+        <v>28</v>
+      </c>
+      <c r="G259" t="n">
+        <v>1426</v>
+      </c>
+      <c r="H259" t="n">
+        <v>50.93</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L259" t="n">
+        <v>1426</v>
+      </c>
+      <c r="M259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>16</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>George W Bush</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>3s2b2okkmdgtlka5</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>28</v>
+      </c>
+      <c r="F260" t="n">
+        <v>26</v>
+      </c>
+      <c r="G260" t="n">
+        <v>1339</v>
+      </c>
+      <c r="H260" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L260" t="n">
+        <v>1339</v>
+      </c>
+      <c r="M260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>16</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>CaitlinClark KeepsItHairy</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>qmjw5ehtmduykj4n</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>28</v>
+      </c>
+      <c r="F261" t="n">
+        <v>33</v>
+      </c>
+      <c r="G261" t="n">
+        <v>1336</v>
+      </c>
+      <c r="H261" t="n">
+        <v>40.48</v>
+      </c>
+      <c r="I261" t="n">
+        <v>5</v>
+      </c>
+      <c r="J261" s="7" t="n">
+        <v>202.4</v>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>15.15%</t>
+        </is>
+      </c>
+      <c r="L261" t="n">
+        <v>1133.6</v>
+      </c>
+      <c r="M261" t="n">
+        <v>-202</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>16</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Jesus Christ</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>zh45p7homdgtlka1</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>28</v>
+      </c>
+      <c r="F262" t="n">
+        <v>25</v>
+      </c>
+      <c r="G262" t="n">
+        <v>1311</v>
+      </c>
+      <c r="H262" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L262" t="n">
+        <v>1311</v>
+      </c>
+      <c r="M262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>17</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Jesus Christ</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>zh45p7homdgtlka1</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>25</v>
+      </c>
+      <c r="F263" t="n">
+        <v>25</v>
+      </c>
+      <c r="G263" t="n">
+        <v>1491</v>
+      </c>
+      <c r="H263" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L263" t="n">
+        <v>1491</v>
+      </c>
+      <c r="M263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>17</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>PartyMarty__</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>oi0ae85dmdmdspm2</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>25</v>
+      </c>
+      <c r="F264" t="n">
+        <v>27</v>
+      </c>
+      <c r="G264" t="n">
+        <v>1485</v>
+      </c>
+      <c r="H264" t="n">
+        <v>55</v>
+      </c>
+      <c r="I264" t="n">
+        <v>2</v>
+      </c>
+      <c r="J264" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>7.41%</t>
+        </is>
+      </c>
+      <c r="L264" t="n">
+        <v>1375</v>
+      </c>
+      <c r="M264" t="n">
+        <v>-110</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>17</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>George W Bush</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>3s2b2okkmdgtlka5</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>25</v>
+      </c>
+      <c r="F265" t="n">
+        <v>26</v>
+      </c>
+      <c r="G265" t="n">
+        <v>1460</v>
+      </c>
+      <c r="H265" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="I265" t="n">
+        <v>1</v>
+      </c>
+      <c r="J265" s="7" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L265" t="n">
+        <v>1403.85</v>
+      </c>
+      <c r="M265" t="n">
+        <v>-56</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>17</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Haliban’s Heroes</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>rhb3mk9hmdgtlka9</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>25</v>
+      </c>
+      <c r="F266" t="n">
+        <v>25</v>
+      </c>
+      <c r="G266" t="n">
+        <v>1448</v>
+      </c>
+      <c r="H266" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L266" t="n">
+        <v>1448</v>
+      </c>
+      <c r="M266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>17</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>I'm Your Uber Driver</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>lc47vt4pmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>25</v>
+      </c>
+      <c r="F267" t="n">
+        <v>25</v>
+      </c>
+      <c r="G267" t="n">
+        <v>1421</v>
+      </c>
+      <c r="H267" t="n">
+        <v>56.84</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L267" t="n">
+        <v>1421</v>
+      </c>
+      <c r="M267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>17</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>The Pentagon</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>wjjl8qwsmdgtlka2</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>25</v>
+      </c>
+      <c r="F268" t="n">
+        <v>27</v>
+      </c>
+      <c r="G268" t="n">
+        <v>1421</v>
+      </c>
+      <c r="H268" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="I268" t="n">
+        <v>2</v>
+      </c>
+      <c r="J268" s="7" t="n">
+        <v>105.26</v>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>7.41%</t>
+        </is>
+      </c>
+      <c r="L268" t="n">
+        <v>1315.74</v>
+      </c>
+      <c r="M268" t="n">
+        <v>-105</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>17</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>The Noto Son</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>zjydlxwhmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>25</v>
+      </c>
+      <c r="F269" t="n">
+        <v>26</v>
+      </c>
+      <c r="G269" t="n">
+        <v>1413</v>
+      </c>
+      <c r="H269" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="I269" t="n">
+        <v>1</v>
+      </c>
+      <c r="J269" s="7" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L269" t="n">
+        <v>1358.65</v>
+      </c>
+      <c r="M269" t="n">
+        <v>-54</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>17</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>LAMELOcan Airlines Flight 11</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>z4ag3f5qmdgtlka8</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>25</v>
+      </c>
+      <c r="F270" t="n">
+        <v>23</v>
+      </c>
+      <c r="G270" t="n">
+        <v>1380</v>
+      </c>
+      <c r="H270" t="n">
+        <v>60</v>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L270" t="n">
+        <v>1380</v>
+      </c>
+      <c r="M270" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>17</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>President of Retarded Operations</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>4trk7d98mdgtlkab</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>25</v>
+      </c>
+      <c r="F271" t="n">
+        <v>25</v>
+      </c>
+      <c r="G271" t="n">
+        <v>1353</v>
+      </c>
+      <c r="H271" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L271" t="n">
+        <v>1353</v>
+      </c>
+      <c r="M271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>17</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Kevin O’Leary</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>467wxistmdgtlka3</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>25</v>
+      </c>
+      <c r="F272" t="n">
+        <v>25</v>
+      </c>
+      <c r="G272" t="n">
+        <v>1307</v>
+      </c>
+      <c r="H272" t="n">
+        <v>52.28</v>
+      </c>
+      <c r="I272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L272" t="n">
+        <v>1307</v>
+      </c>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>17</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>9/11 First Tower</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>dmx5bjkpmdgtlkab</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>25</v>
+      </c>
+      <c r="F273" t="n">
+        <v>25</v>
+      </c>
+      <c r="G273" t="n">
+        <v>1233</v>
+      </c>
+      <c r="H273" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L273" t="n">
+        <v>1233</v>
+      </c>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>17</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>9/11 Second Tower</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>68fvh5u4mdgtlka8</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>25</v>
+      </c>
+      <c r="F274" t="n">
+        <v>25</v>
+      </c>
+      <c r="G274" t="n">
+        <v>1227</v>
+      </c>
+      <c r="H274" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L274" t="n">
+        <v>1227</v>
+      </c>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>17</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Kamala's Gunz</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>hxzn4i3jmdgtlka7</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>25</v>
+      </c>
+      <c r="F275" t="n">
+        <v>24</v>
+      </c>
+      <c r="G275" t="n">
+        <v>1226</v>
+      </c>
+      <c r="H275" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="I275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L275" t="n">
+        <v>1226</v>
+      </c>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>17</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Daaaaaa Jankees lose</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>7wets94rmdgtlkaa</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>25</v>
+      </c>
+      <c r="F276" t="n">
+        <v>24</v>
+      </c>
+      <c r="G276" t="n">
+        <v>1215</v>
+      </c>
+      <c r="H276" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="I276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L276" t="n">
+        <v>1215</v>
+      </c>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>17</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>CaitlinClark KeepsItHairy</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>qmjw5ehtmduykj4n</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>25</v>
+      </c>
+      <c r="F277" t="n">
+        <v>26</v>
+      </c>
+      <c r="G277" t="n">
+        <v>1213</v>
+      </c>
+      <c r="H277" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="I277" t="n">
+        <v>1</v>
+      </c>
+      <c r="J277" s="7" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L277" t="n">
+        <v>1166.35</v>
+      </c>
+      <c r="M277" t="n">
+        <v>-47</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>17</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>A Stupid Silly Cat</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>0l1gmqj7mdgtlka6</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>25</v>
+      </c>
+      <c r="F278" t="n">
+        <v>26</v>
+      </c>
+      <c r="G278" t="n">
+        <v>1159</v>
+      </c>
+      <c r="H278" t="n">
+        <v>44.58</v>
+      </c>
+      <c r="I278" t="n">
+        <v>1</v>
+      </c>
+      <c r="J278" s="7" t="n">
+        <v>44.58</v>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L278" t="n">
+        <v>1114.42</v>
+      </c>
+      <c r="M278" t="n">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>18</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Jesus Christ</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>zh45p7homdgtlka1</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>25</v>
+      </c>
+      <c r="F279" t="n">
+        <v>27</v>
+      </c>
+      <c r="G279" t="n">
+        <v>1774</v>
+      </c>
+      <c r="H279" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="I279" t="n">
+        <v>2</v>
+      </c>
+      <c r="J279" s="7" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>7.41%</t>
+        </is>
+      </c>
+      <c r="L279" t="n">
+        <v>1642.6</v>
+      </c>
+      <c r="M279" t="n">
+        <v>-131</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>18</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>The Noto Son</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>zjydlxwhmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>25</v>
+      </c>
+      <c r="F280" t="n">
+        <v>25</v>
+      </c>
+      <c r="G280" t="n">
+        <v>1670</v>
+      </c>
+      <c r="H280" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="I280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L280" t="n">
+        <v>1670</v>
+      </c>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>18</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>The Pentagon</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>wjjl8qwsmdgtlka2</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>25</v>
+      </c>
+      <c r="F281" t="n">
+        <v>26</v>
+      </c>
+      <c r="G281" t="n">
+        <v>1666</v>
+      </c>
+      <c r="H281" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="I281" t="n">
+        <v>1</v>
+      </c>
+      <c r="J281" s="7" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L281" t="n">
+        <v>1601.92</v>
+      </c>
+      <c r="M281" t="n">
+        <v>-64</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>18</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Kevin O’Leary</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>467wxistmdgtlka3</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>25</v>
+      </c>
+      <c r="F282" t="n">
+        <v>25</v>
+      </c>
+      <c r="G282" t="n">
+        <v>1460</v>
+      </c>
+      <c r="H282" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="I282" t="n">
+        <v>0</v>
+      </c>
+      <c r="J282" t="n">
+        <v>0</v>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L282" t="n">
+        <v>1460</v>
+      </c>
+      <c r="M282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>18</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>PartyMarty__</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>oi0ae85dmdmdspm2</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>25</v>
+      </c>
+      <c r="F283" t="n">
+        <v>28</v>
+      </c>
+      <c r="G283" t="n">
+        <v>1440</v>
+      </c>
+      <c r="H283" t="n">
+        <v>51.43</v>
+      </c>
+      <c r="I283" t="n">
+        <v>3</v>
+      </c>
+      <c r="J283" s="7" t="n">
+        <v>154.29</v>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>10.71%</t>
+        </is>
+      </c>
+      <c r="L283" t="n">
+        <v>1285.71</v>
+      </c>
+      <c r="M283" t="n">
+        <v>-154</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>18</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>LAMELOcan Airlines Flight 11</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>z4ag3f5qmdgtlka8</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>25</v>
+      </c>
+      <c r="F284" t="n">
+        <v>26</v>
+      </c>
+      <c r="G284" t="n">
+        <v>1417</v>
+      </c>
+      <c r="H284" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="I284" t="n">
+        <v>1</v>
+      </c>
+      <c r="J284" s="7" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L284" t="n">
+        <v>1362.5</v>
+      </c>
+      <c r="M284" t="n">
+        <v>-54</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>18</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>I'm Your Uber Driver</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>lc47vt4pmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>25</v>
+      </c>
+      <c r="F285" t="n">
+        <v>25</v>
+      </c>
+      <c r="G285" t="n">
+        <v>1387</v>
+      </c>
+      <c r="H285" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L285" t="n">
+        <v>1387</v>
+      </c>
+      <c r="M285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>18</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>CaitlinClark KeepsItHairy</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>qmjw5ehtmduykj4n</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>25</v>
+      </c>
+      <c r="F286" t="n">
+        <v>29</v>
+      </c>
+      <c r="G286" t="n">
+        <v>1380</v>
+      </c>
+      <c r="H286" t="n">
+        <v>47.59</v>
+      </c>
+      <c r="I286" t="n">
+        <v>4</v>
+      </c>
+      <c r="J286" s="7" t="n">
+        <v>190.36</v>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>13.79%</t>
+        </is>
+      </c>
+      <c r="L286" t="n">
+        <v>1189.64</v>
+      </c>
+      <c r="M286" t="n">
+        <v>-190</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>18</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Haliban’s Heroes</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>rhb3mk9hmdgtlka9</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>25</v>
+      </c>
+      <c r="F287" t="n">
+        <v>24</v>
+      </c>
+      <c r="G287" t="n">
+        <v>1350</v>
+      </c>
+      <c r="H287" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="I287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0</v>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L287" t="n">
+        <v>1350</v>
+      </c>
+      <c r="M287" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>18</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>George W Bush</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>3s2b2okkmdgtlka5</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>25</v>
+      </c>
+      <c r="F288" t="n">
+        <v>28</v>
+      </c>
+      <c r="G288" t="n">
+        <v>1343</v>
+      </c>
+      <c r="H288" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="I288" t="n">
+        <v>3</v>
+      </c>
+      <c r="J288" s="7" t="n">
+        <v>143.88</v>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>10.71%</t>
+        </is>
+      </c>
+      <c r="L288" t="n">
+        <v>1199.12</v>
+      </c>
+      <c r="M288" t="n">
+        <v>-144</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>18</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>President of Retarded Operations</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>4trk7d98mdgtlkab</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>25</v>
+      </c>
+      <c r="F289" t="n">
+        <v>25</v>
+      </c>
+      <c r="G289" t="n">
+        <v>1268</v>
+      </c>
+      <c r="H289" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L289" t="n">
+        <v>1268</v>
+      </c>
+      <c r="M289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>18</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>9/11 Second Tower</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>68fvh5u4mdgtlka8</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>25</v>
+      </c>
+      <c r="F290" t="n">
+        <v>26</v>
+      </c>
+      <c r="G290" t="n">
+        <v>1259</v>
+      </c>
+      <c r="H290" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="I290" t="n">
+        <v>1</v>
+      </c>
+      <c r="J290" s="7" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L290" t="n">
+        <v>1210.58</v>
+      </c>
+      <c r="M290" t="n">
+        <v>-48</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>18</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>9/11 First Tower</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>dmx5bjkpmdgtlkab</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>25</v>
+      </c>
+      <c r="F291" t="n">
+        <v>22</v>
+      </c>
+      <c r="G291" t="n">
+        <v>1250</v>
+      </c>
+      <c r="H291" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L291" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>18</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>A Stupid Silly Cat</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>0l1gmqj7mdgtlka6</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>25</v>
+      </c>
+      <c r="F292" t="n">
+        <v>25</v>
+      </c>
+      <c r="G292" t="n">
+        <v>1217</v>
+      </c>
+      <c r="H292" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="n">
+        <v>0</v>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L292" t="n">
+        <v>1217</v>
+      </c>
+      <c r="M292" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>18</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Daaaaaa Jankees lose</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>7wets94rmdgtlkaa</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>25</v>
+      </c>
+      <c r="F293" t="n">
+        <v>27</v>
+      </c>
+      <c r="G293" t="n">
+        <v>1168</v>
+      </c>
+      <c r="H293" t="n">
+        <v>43.26</v>
+      </c>
+      <c r="I293" t="n">
+        <v>2</v>
+      </c>
+      <c r="J293" s="7" t="n">
+        <v>86.52</v>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>7.41%</t>
+        </is>
+      </c>
+      <c r="L293" t="n">
+        <v>1081.48</v>
+      </c>
+      <c r="M293" t="n">
+        <v>-87</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>18</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Kamala's Gunz</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>hxzn4i3jmdgtlka7</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>25</v>
+      </c>
+      <c r="F294" t="n">
+        <v>23</v>
+      </c>
+      <c r="G294" t="n">
+        <v>947</v>
+      </c>
+      <c r="H294" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="I294" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L294" t="n">
+        <v>947</v>
+      </c>
+      <c r="M294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>19</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>The Noto Son</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>zjydlxwhmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>25</v>
+      </c>
+      <c r="F295" t="n">
+        <v>26</v>
+      </c>
+      <c r="G295" t="n">
+        <v>1714</v>
+      </c>
+      <c r="H295" t="n">
+        <v>65.92</v>
+      </c>
+      <c r="I295" t="n">
+        <v>1</v>
+      </c>
+      <c r="J295" s="7" t="n">
+        <v>65.92</v>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L295" t="n">
+        <v>1648.08</v>
+      </c>
+      <c r="M295" t="n">
+        <v>-66</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>19</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>A Stupid Silly Cat</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>0l1gmqj7mdgtlka6</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>25</v>
+      </c>
+      <c r="F296" t="n">
+        <v>25</v>
+      </c>
+      <c r="G296" t="n">
+        <v>1653</v>
+      </c>
+      <c r="H296" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="I296" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L296" t="n">
+        <v>1653</v>
+      </c>
+      <c r="M296" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>19</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>President of Retarded Operations</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>4trk7d98mdgtlkab</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>25</v>
+      </c>
+      <c r="F297" t="n">
+        <v>29</v>
+      </c>
+      <c r="G297" t="n">
+        <v>1641</v>
+      </c>
+      <c r="H297" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="I297" t="n">
+        <v>4</v>
+      </c>
+      <c r="J297" s="7" t="n">
+        <v>226.36</v>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>13.79%</t>
+        </is>
+      </c>
+      <c r="L297" t="n">
+        <v>1414.64</v>
+      </c>
+      <c r="M297" t="n">
+        <v>-226</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>19</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Jesus Christ</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>zh45p7homdgtlka1</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>25</v>
+      </c>
+      <c r="F298" t="n">
+        <v>25</v>
+      </c>
+      <c r="G298" t="n">
+        <v>1634</v>
+      </c>
+      <c r="H298" t="n">
+        <v>65.36</v>
+      </c>
+      <c r="I298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L298" t="n">
+        <v>1634</v>
+      </c>
+      <c r="M298" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>19</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>The Pentagon</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>wjjl8qwsmdgtlka2</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>25</v>
+      </c>
+      <c r="F299" t="n">
+        <v>25</v>
+      </c>
+      <c r="G299" t="n">
+        <v>1567</v>
+      </c>
+      <c r="H299" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="I299" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L299" t="n">
+        <v>1567</v>
+      </c>
+      <c r="M299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>19</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Haliban’s Heroes</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>rhb3mk9hmdgtlka9</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>25</v>
+      </c>
+      <c r="F300" t="n">
+        <v>25</v>
+      </c>
+      <c r="G300" t="n">
+        <v>1529</v>
+      </c>
+      <c r="H300" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="I300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L300" t="n">
+        <v>1529</v>
+      </c>
+      <c r="M300" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>19</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Kevin O’Leary</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>467wxistmdgtlka3</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>25</v>
+      </c>
+      <c r="F301" t="n">
+        <v>25</v>
+      </c>
+      <c r="G301" t="n">
+        <v>1462</v>
+      </c>
+      <c r="H301" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="I301" t="n">
+        <v>0</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L301" t="n">
+        <v>1462</v>
+      </c>
+      <c r="M301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>19</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>LAMELOcan Airlines Flight 11</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>z4ag3f5qmdgtlka8</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>25</v>
+      </c>
+      <c r="F302" t="n">
+        <v>24</v>
+      </c>
+      <c r="G302" t="n">
+        <v>1447</v>
+      </c>
+      <c r="H302" t="n">
+        <v>60.29</v>
+      </c>
+      <c r="I302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L302" t="n">
+        <v>1447</v>
+      </c>
+      <c r="M302" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>19</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Daaaaaa Jankees lose</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>7wets94rmdgtlkaa</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>25</v>
+      </c>
+      <c r="F303" t="n">
+        <v>29</v>
+      </c>
+      <c r="G303" t="n">
+        <v>1382</v>
+      </c>
+      <c r="H303" t="n">
+        <v>47.66</v>
+      </c>
+      <c r="I303" t="n">
+        <v>4</v>
+      </c>
+      <c r="J303" s="7" t="n">
+        <v>190.64</v>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>13.79%</t>
+        </is>
+      </c>
+      <c r="L303" t="n">
+        <v>1191.36</v>
+      </c>
+      <c r="M303" t="n">
+        <v>-191</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>19</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Kamala's Gunz</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>hxzn4i3jmdgtlka7</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>25</v>
+      </c>
+      <c r="F304" t="n">
+        <v>25</v>
+      </c>
+      <c r="G304" t="n">
+        <v>1382</v>
+      </c>
+      <c r="H304" t="n">
+        <v>55.28</v>
+      </c>
+      <c r="I304" t="n">
+        <v>0</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L304" t="n">
+        <v>1382</v>
+      </c>
+      <c r="M304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>19</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>I'm Your Uber Driver</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>lc47vt4pmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>25</v>
+      </c>
+      <c r="F305" t="n">
+        <v>25</v>
+      </c>
+      <c r="G305" t="n">
+        <v>1375</v>
+      </c>
+      <c r="H305" t="n">
+        <v>55</v>
+      </c>
+      <c r="I305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L305" t="n">
+        <v>1375</v>
+      </c>
+      <c r="M305" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>19</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>9/11 First Tower</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>dmx5bjkpmdgtlkab</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>25</v>
+      </c>
+      <c r="F306" t="n">
+        <v>25</v>
+      </c>
+      <c r="G306" t="n">
+        <v>1265</v>
+      </c>
+      <c r="H306" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="I306" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L306" t="n">
+        <v>1265</v>
+      </c>
+      <c r="M306" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>19</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>CaitlinClark KeepsItHairy</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>qmjw5ehtmduykj4n</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>25</v>
+      </c>
+      <c r="F307" t="n">
+        <v>27</v>
+      </c>
+      <c r="G307" t="n">
+        <v>1251</v>
+      </c>
+      <c r="H307" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="I307" t="n">
+        <v>2</v>
+      </c>
+      <c r="J307" s="7" t="n">
+        <v>92.66</v>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>7.41%</t>
+        </is>
+      </c>
+      <c r="L307" t="n">
+        <v>1158.34</v>
+      </c>
+      <c r="M307" t="n">
+        <v>-93</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>19</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>9/11 Second Tower</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>68fvh5u4mdgtlka8</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>25</v>
+      </c>
+      <c r="F308" t="n">
+        <v>26</v>
+      </c>
+      <c r="G308" t="n">
+        <v>1239</v>
+      </c>
+      <c r="H308" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="I308" t="n">
+        <v>1</v>
+      </c>
+      <c r="J308" s="7" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L308" t="n">
+        <v>1191.35</v>
+      </c>
+      <c r="M308" t="n">
+        <v>-48</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>19</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>George W Bush</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>3s2b2okkmdgtlka5</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>25</v>
+      </c>
+      <c r="F309" t="n">
+        <v>24</v>
+      </c>
+      <c r="G309" t="n">
+        <v>1180</v>
+      </c>
+      <c r="H309" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="I309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" t="n">
+        <v>0</v>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L309" t="n">
+        <v>1180</v>
+      </c>
+      <c r="M309" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>19</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>PartyMarty__</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>oi0ae85dmdmdspm2</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>25</v>
+      </c>
+      <c r="F310" t="n">
+        <v>19</v>
+      </c>
+      <c r="G310" t="n">
+        <v>1107</v>
+      </c>
+      <c r="H310" t="n">
+        <v>58.26</v>
+      </c>
+      <c r="I310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" t="n">
+        <v>0</v>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L310" t="n">
+        <v>1107</v>
+      </c>
+      <c r="M310" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>20</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Jesus Christ</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>zh45p7homdgtlka1</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>25</v>
+      </c>
+      <c r="F311" t="n">
+        <v>25</v>
+      </c>
+      <c r="G311" t="n">
+        <v>1623</v>
+      </c>
+      <c r="H311" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="I311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L311" t="n">
+        <v>1623</v>
+      </c>
+      <c r="M311" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>20</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>George W Bush</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>3s2b2okkmdgtlka5</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>25</v>
+      </c>
+      <c r="F312" t="n">
+        <v>32</v>
+      </c>
+      <c r="G312" t="n">
+        <v>1585</v>
+      </c>
+      <c r="H312" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="I312" t="n">
+        <v>7</v>
+      </c>
+      <c r="J312" s="7" t="n">
+        <v>346.71</v>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>21.87%</t>
+        </is>
+      </c>
+      <c r="L312" t="n">
+        <v>1238.29</v>
+      </c>
+      <c r="M312" t="n">
+        <v>-347</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>20</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>The Pentagon</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>wjjl8qwsmdgtlka2</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>25</v>
+      </c>
+      <c r="F313" t="n">
+        <v>26</v>
+      </c>
+      <c r="G313" t="n">
+        <v>1577</v>
+      </c>
+      <c r="H313" t="n">
+        <v>60.65</v>
+      </c>
+      <c r="I313" t="n">
+        <v>1</v>
+      </c>
+      <c r="J313" s="7" t="n">
+        <v>60.65</v>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="L313" t="n">
+        <v>1516.35</v>
+      </c>
+      <c r="M313" t="n">
+        <v>-61</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>20</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>The Noto Son</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>zjydlxwhmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>25</v>
+      </c>
+      <c r="F314" t="n">
+        <v>25</v>
+      </c>
+      <c r="G314" t="n">
+        <v>1544</v>
+      </c>
+      <c r="H314" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="I314" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" t="n">
+        <v>0</v>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L314" t="n">
+        <v>1544</v>
+      </c>
+      <c r="M314" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>20</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>CaitlinClark KeepsItHairy</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>qmjw5ehtmduykj4n</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>25</v>
+      </c>
+      <c r="F315" t="n">
+        <v>28</v>
+      </c>
+      <c r="G315" t="n">
+        <v>1434</v>
+      </c>
+      <c r="H315" t="n">
+        <v>51.21</v>
+      </c>
+      <c r="I315" t="n">
+        <v>3</v>
+      </c>
+      <c r="J315" s="7" t="n">
+        <v>153.63</v>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>10.71%</t>
+        </is>
+      </c>
+      <c r="L315" t="n">
+        <v>1280.37</v>
+      </c>
+      <c r="M315" t="n">
+        <v>-154</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>20</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>9/11 First Tower</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>dmx5bjkpmdgtlkab</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>25</v>
+      </c>
+      <c r="F316" t="n">
+        <v>31</v>
+      </c>
+      <c r="G316" t="n">
+        <v>1432</v>
+      </c>
+      <c r="H316" t="n">
+        <v>46.19</v>
+      </c>
+      <c r="I316" t="n">
+        <v>6</v>
+      </c>
+      <c r="J316" s="7" t="n">
+        <v>277.14</v>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>19.35%</t>
+        </is>
+      </c>
+      <c r="L316" t="n">
+        <v>1154.86</v>
+      </c>
+      <c r="M316" t="n">
+        <v>-277</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>20</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>A Stupid Silly Cat</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>0l1gmqj7mdgtlka6</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>25</v>
+      </c>
+      <c r="F317" t="n">
+        <v>25</v>
+      </c>
+      <c r="G317" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H317" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="I317" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L317" t="n">
+        <v>1420</v>
+      </c>
+      <c r="M317" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>20</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Kevin O’Leary</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>467wxistmdgtlka3</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>25</v>
+      </c>
+      <c r="F318" t="n">
+        <v>24</v>
+      </c>
+      <c r="G318" t="n">
+        <v>1374</v>
+      </c>
+      <c r="H318" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="I318" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" t="n">
+        <v>0</v>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L318" t="n">
+        <v>1374</v>
+      </c>
+      <c r="M318" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>20</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>9/11 Second Tower</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>68fvh5u4mdgtlka8</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>25</v>
+      </c>
+      <c r="F319" t="n">
+        <v>22</v>
+      </c>
+      <c r="G319" t="n">
+        <v>1276</v>
+      </c>
+      <c r="H319" t="n">
+        <v>58</v>
+      </c>
+      <c r="I319" t="n">
+        <v>0</v>
+      </c>
+      <c r="J319" t="n">
+        <v>0</v>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L319" t="n">
+        <v>1276</v>
+      </c>
+      <c r="M319" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>20</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Daaaaaa Jankees lose</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>7wets94rmdgtlkaa</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>25</v>
+      </c>
+      <c r="F320" t="n">
+        <v>25</v>
+      </c>
+      <c r="G320" t="n">
+        <v>1271</v>
+      </c>
+      <c r="H320" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="I320" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" t="n">
+        <v>0</v>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L320" t="n">
+        <v>1271</v>
+      </c>
+      <c r="M320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>20</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Haliban’s Heroes</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>rhb3mk9hmdgtlka9</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>25</v>
+      </c>
+      <c r="F321" t="n">
+        <v>25</v>
+      </c>
+      <c r="G321" t="n">
+        <v>1266</v>
+      </c>
+      <c r="H321" t="n">
+        <v>50.64</v>
+      </c>
+      <c r="I321" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" t="n">
+        <v>0</v>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L321" t="n">
+        <v>1266</v>
+      </c>
+      <c r="M321" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>20</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>I'm Your Uber Driver</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>lc47vt4pmdgtlka4</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>25</v>
+      </c>
+      <c r="F322" t="n">
+        <v>25</v>
+      </c>
+      <c r="G322" t="n">
+        <v>1255</v>
+      </c>
+      <c r="H322" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="I322" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" t="n">
+        <v>0</v>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L322" t="n">
+        <v>1255</v>
+      </c>
+      <c r="M322" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>20</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>President of Retarded Operations</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>4trk7d98mdgtlkab</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>25</v>
+      </c>
+      <c r="F323" t="n">
+        <v>19</v>
+      </c>
+      <c r="G323" t="n">
+        <v>1205</v>
+      </c>
+      <c r="H323" t="n">
+        <v>63.42</v>
+      </c>
+      <c r="I323" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" t="n">
+        <v>0</v>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L323" t="n">
+        <v>1205</v>
+      </c>
+      <c r="M323" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>20</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Kamala's Gunz</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>hxzn4i3jmdgtlka7</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>25</v>
+      </c>
+      <c r="F324" t="n">
+        <v>25</v>
+      </c>
+      <c r="G324" t="n">
+        <v>1183</v>
+      </c>
+      <c r="H324" t="n">
+        <v>47.32</v>
+      </c>
+      <c r="I324" t="n">
+        <v>0</v>
+      </c>
+      <c r="J324" t="n">
+        <v>0</v>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L324" t="n">
+        <v>1183</v>
+      </c>
+      <c r="M324" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>20</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>PartyMarty__</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>oi0ae85dmdmdspm2</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>25</v>
+      </c>
+      <c r="F325" t="n">
+        <v>22</v>
+      </c>
+      <c r="G325" t="n">
+        <v>1153</v>
+      </c>
+      <c r="H325" t="n">
+        <v>52.41</v>
+      </c>
+      <c r="I325" t="n">
+        <v>0</v>
+      </c>
+      <c r="J325" t="n">
+        <v>0</v>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L325" t="n">
+        <v>1153</v>
+      </c>
+      <c r="M325" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>20</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>LAMELOcan Airlines Flight 11</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>z4ag3f5qmdgtlka8</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>25</v>
+      </c>
+      <c r="F326" t="n">
+        <v>21</v>
+      </c>
+      <c r="G326" t="n">
+        <v>1112</v>
+      </c>
+      <c r="H326" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="n">
+        <v>0</v>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L326" t="n">
+        <v>1112</v>
+      </c>
+      <c r="M326" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
@@ -10796,7 +16284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="5" min="1" max="7"/>
@@ -11171,6 +16659,181 @@
         <v>215.65</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:21:33</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>612.22</v>
+      </c>
+      <c r="F17" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="G17" t="n">
+        <v>256.08</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-02-08 17:56:49</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>370.07</v>
+      </c>
+      <c r="F18" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="G18" t="n">
+        <v>114.22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-02-22 23:59:41</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>28</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>533.21</v>
+      </c>
+      <c r="F19" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="G19" t="n">
+        <v>202.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-01 23:57:21</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>416.99</v>
+      </c>
+      <c r="F20" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="G20" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-09 02:05:27</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>25</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>873.45</v>
+      </c>
+      <c r="F21" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="G21" t="n">
+        <v>190.36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:32:00</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>623.23</v>
+      </c>
+      <c r="F22" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="G22" t="n">
+        <v>226.36</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-22 23:35:33</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>25</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>838.13</v>
+      </c>
+      <c r="F23" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="G23" t="n">
+        <v>346.71</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
